--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784644</v>
+        <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92483</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413901</v>
+        <v>413934</v>
       </c>
       <c r="R3" t="n">
-        <v>6966647</v>
+        <v>6966721</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/136827979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7000385</v>
+        <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>78993</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413721</v>
+        <v>413901</v>
       </c>
       <c r="R4" t="n">
-        <v>6966650</v>
+        <v>6966580</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,69 +969,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/136827988</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7000395</v>
+        <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413789</v>
+        <v>413901</v>
       </c>
       <c r="R5" t="n">
-        <v>6966542</v>
+        <v>6966501</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,69 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/136827992</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7000396</v>
+        <v>135784644</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>92483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413808</v>
+        <v>413901</v>
       </c>
       <c r="R6" t="n">
-        <v>6966558</v>
+        <v>6966647</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,28 +1173,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7000397</v>
+        <v>7000385</v>
       </c>
       <c r="B7" t="n">
         <v>78993</v>
@@ -1237,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413821</v>
+        <v>413721</v>
       </c>
       <c r="R7" t="n">
-        <v>6966543</v>
+        <v>6966650</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1272,7 +1260,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,54 +1290,54 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135784642</v>
+        <v>7000395</v>
       </c>
       <c r="B8" t="n">
-        <v>92267</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413742</v>
+        <v>413789</v>
       </c>
       <c r="R8" t="n">
-        <v>6966614</v>
+        <v>6966542</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,27 +1381,31 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784639</v>
+        <v>7000396</v>
       </c>
       <c r="B9" t="n">
-        <v>92281</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,37 +1413,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413741</v>
+        <v>413808</v>
       </c>
       <c r="R9" t="n">
-        <v>6966620</v>
+        <v>6966558</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,27 +1487,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7000406</v>
+        <v>7000397</v>
       </c>
       <c r="B10" t="n">
-        <v>90932</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414049</v>
+        <v>413821</v>
       </c>
       <c r="R10" t="n">
-        <v>6966529</v>
+        <v>6966543</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1582,7 +1578,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,16 +1608,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135784649</v>
+        <v>136827974</v>
       </c>
       <c r="B11" t="n">
-        <v>91097</v>
+        <v>79142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,37 +1625,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413926</v>
+        <v>414021</v>
       </c>
       <c r="R11" t="n">
-        <v>6966725</v>
+        <v>6966557</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,12 +1679,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,27 +1699,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/136827974</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120096941</v>
+        <v>136827975</v>
       </c>
       <c r="B12" t="n">
-        <v>91962</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,13 +1751,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413934</v>
+        <v>414010</v>
       </c>
       <c r="R12" t="n">
-        <v>6966582</v>
+        <v>6966573</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1781,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,27 +1801,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/136827975</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120096943</v>
+        <v>136827977</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>79142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,13 +1853,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413950</v>
+        <v>414020</v>
       </c>
       <c r="R13" t="n">
-        <v>6966665</v>
+        <v>6966636</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,22 +1883,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,27 +1903,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/136827977</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120096944</v>
+        <v>136827980</v>
       </c>
       <c r="B14" t="n">
-        <v>91962</v>
+        <v>79142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,13 +1955,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R14" t="n">
-        <v>6966758</v>
+        <v>6966746</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,22 +1985,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,27 +2005,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/136827980</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135784638</v>
+        <v>136827981</v>
       </c>
       <c r="B15" t="n">
-        <v>92010</v>
+        <v>79142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,37 +2033,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413740</v>
+        <v>413888</v>
       </c>
       <c r="R15" t="n">
-        <v>6966625</v>
+        <v>6966757</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2121,12 +2087,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,65 +2107,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
+          <t>https://artportalen.se/Sighting/136827981</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784640</v>
+        <v>136827987</v>
       </c>
       <c r="B16" t="n">
-        <v>92051</v>
+        <v>79142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413742</v>
+        <v>413928</v>
       </c>
       <c r="R16" t="n">
-        <v>6966614</v>
+        <v>6966597</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,12 +2189,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,27 +2209,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
+          <t>https://artportalen.se/Sighting/136827987</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120096988</v>
+        <v>136827990</v>
       </c>
       <c r="B17" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2237,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,13 +2261,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413934</v>
+        <v>413884</v>
       </c>
       <c r="R17" t="n">
-        <v>6966582</v>
+        <v>6966525</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,22 +2291,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,27 +2311,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
+          <t>https://artportalen.se/Sighting/136827990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120096989</v>
+        <v>136827991</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,13 +2363,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R18" t="n">
-        <v>6966758</v>
+        <v>6966496</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,22 +2393,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2467,27 +2413,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
+          <t>https://artportalen.se/Sighting/136827991</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120096990</v>
+        <v>136827997</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,13 +2465,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413973</v>
+        <v>413700</v>
       </c>
       <c r="R19" t="n">
-        <v>6966788</v>
+        <v>6966474</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,22 +2495,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,49 +2515,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
+          <t>https://artportalen.se/Sighting/136827997</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135784646</v>
+        <v>135784642</v>
       </c>
       <c r="B20" t="n">
-        <v>78863</v>
+        <v>92267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413899</v>
+        <v>413742</v>
       </c>
       <c r="R20" t="n">
-        <v>6966659</v>
+        <v>6966614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,54 +2628,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784635</v>
+        <v>136827978</v>
       </c>
       <c r="B21" t="n">
-        <v>80079</v>
+        <v>92292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413755</v>
+        <v>414001</v>
       </c>
       <c r="R21" t="n">
-        <v>6966653</v>
+        <v>6966632</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2763,12 +2699,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2783,27 +2719,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
+          <t>https://artportalen.se/Sighting/136827978</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135784637</v>
+        <v>135784639</v>
       </c>
       <c r="B22" t="n">
-        <v>80079</v>
+        <v>92281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2747,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413752</v>
+        <v>413741</v>
       </c>
       <c r="R22" t="n">
-        <v>6966651</v>
+        <v>6966620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,16 +2832,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120096980</v>
+        <v>7000406</v>
       </c>
       <c r="B23" t="n">
-        <v>78334</v>
+        <v>90932</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,37 +2849,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413968</v>
+        <v>414049</v>
       </c>
       <c r="R23" t="n">
-        <v>6966758</v>
+        <v>6966529</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2967,22 +2903,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,27 +2923,31 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135784647</v>
+        <v>135784649</v>
       </c>
       <c r="B24" t="n">
-        <v>78464</v>
+        <v>91097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>413899</v>
+        <v>413926</v>
       </c>
       <c r="R24" t="n">
-        <v>6966658</v>
+        <v>6966725</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,38 +3040,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120096936</v>
+        <v>120096941</v>
       </c>
       <c r="B25" t="n">
-        <v>97989</v>
+        <v>91962</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413957</v>
+        <v>413934</v>
       </c>
       <c r="R25" t="n">
-        <v>6966625</v>
+        <v>6966582</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,7 +3116,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3196,7 +3126,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3222,16 +3152,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135784636</v>
+        <v>120096943</v>
       </c>
       <c r="B26" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,34 +3169,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413755</v>
+        <v>413950</v>
       </c>
       <c r="R26" t="n">
-        <v>6966653</v>
+        <v>6966665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,12 +3223,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3313,27 +3253,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135784645</v>
+        <v>120096944</v>
       </c>
       <c r="B27" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,34 +3281,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413897</v>
+        <v>413968</v>
       </c>
       <c r="R27" t="n">
-        <v>6966658</v>
+        <v>6966758</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,12 +3335,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3415,27 +3365,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120096926</v>
+        <v>136827986</v>
       </c>
       <c r="B28" t="n">
-        <v>79917</v>
+        <v>92166</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3443,21 +3393,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3467,13 +3417,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413968</v>
+        <v>413898</v>
       </c>
       <c r="R28" t="n">
-        <v>6966758</v>
+        <v>6966645</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3497,22 +3447,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3527,18 +3467,2424 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136827986</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135784638</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92010</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>413740</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784638</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135784640</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92051</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>413742</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784640</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136827989</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>413901</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6966581</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827989</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120096988</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096988</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120096989</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096989</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120096990</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>413973</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6966788</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096990</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135784646</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78863</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6966659</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784646</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136827983</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>413867</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6966631</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827983</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136827995</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>413694</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6966470</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827995</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135784635</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784635</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135784637</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>413752</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784637</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136827976</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>414019</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827976</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120096980</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096980</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135784647</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784647</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136827984</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>413898</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6966647</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827984</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136827993</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>413765</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6966461</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827993</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120096936</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>413957</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096936</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135784636</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784636</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135784645</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>413897</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784645</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136827985</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>413903</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827985</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120096926</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136827982</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>413834</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6966671</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827982</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136827994</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>413748</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6966466</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -3571,6 +5917,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,48 +1190,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7000385</v>
+        <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>92508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413721</v>
+        <v>413693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966650</v>
+        <v>6966468</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,34 +1272,31 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000395</v>
+        <v>7000385</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413789</v>
+        <v>413721</v>
       </c>
       <c r="R8" t="n">
-        <v>6966542</v>
+        <v>6966650</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,13 +1396,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7000396</v>
+        <v>7000395</v>
       </c>
       <c r="B9" t="n">
         <v>78993</v>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413808</v>
+        <v>413789</v>
       </c>
       <c r="R9" t="n">
-        <v>6966558</v>
+        <v>6966542</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1502,13 +1502,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7000397</v>
+        <v>7000396</v>
       </c>
       <c r="B10" t="n">
         <v>78993</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413821</v>
+        <v>413808</v>
       </c>
       <c r="R10" t="n">
-        <v>6966543</v>
+        <v>6966558</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,16 +1608,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136827974</v>
+        <v>7000397</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,17 +1645,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414021</v>
+        <v>413821</v>
       </c>
       <c r="R11" t="n">
-        <v>6966557</v>
+        <v>6966543</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,24 +1699,28 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827974</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136827975</v>
+        <v>136827974</v>
       </c>
       <c r="B12" t="n">
         <v>79142</v>
@@ -1751,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414010</v>
+        <v>414021</v>
       </c>
       <c r="R12" t="n">
-        <v>6966573</v>
+        <v>6966557</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1812,13 +1816,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827975</t>
+          <t>https://artportalen.se/Sighting/136827974</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136827977</v>
+        <v>136827975</v>
       </c>
       <c r="B13" t="n">
         <v>79142</v>
@@ -1853,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414020</v>
+        <v>414010</v>
       </c>
       <c r="R13" t="n">
-        <v>6966636</v>
+        <v>6966573</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1914,13 +1918,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827977</t>
+          <t>https://artportalen.se/Sighting/136827975</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136827980</v>
+        <v>136827977</v>
       </c>
       <c r="B14" t="n">
         <v>79142</v>
@@ -1955,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413902</v>
+        <v>414020</v>
       </c>
       <c r="R14" t="n">
-        <v>6966746</v>
+        <v>6966636</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2016,13 +2020,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827980</t>
+          <t>https://artportalen.se/Sighting/136827977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136827981</v>
+        <v>136827980</v>
       </c>
       <c r="B15" t="n">
         <v>79142</v>
@@ -2057,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413888</v>
+        <v>413902</v>
       </c>
       <c r="R15" t="n">
-        <v>6966757</v>
+        <v>6966746</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2118,13 +2122,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827981</t>
+          <t>https://artportalen.se/Sighting/136827980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136827987</v>
+        <v>136827981</v>
       </c>
       <c r="B16" t="n">
         <v>79142</v>
@@ -2159,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413928</v>
+        <v>413888</v>
       </c>
       <c r="R16" t="n">
-        <v>6966597</v>
+        <v>6966757</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2220,13 +2224,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827987</t>
+          <t>https://artportalen.se/Sighting/136827981</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136827990</v>
+        <v>136827987</v>
       </c>
       <c r="B17" t="n">
         <v>79142</v>
@@ -2261,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413884</v>
+        <v>413928</v>
       </c>
       <c r="R17" t="n">
-        <v>6966525</v>
+        <v>6966597</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2322,13 +2326,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827990</t>
+          <t>https://artportalen.se/Sighting/136827987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136827991</v>
+        <v>136827990</v>
       </c>
       <c r="B18" t="n">
         <v>79142</v>
@@ -2363,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413902</v>
+        <v>413884</v>
       </c>
       <c r="R18" t="n">
-        <v>6966496</v>
+        <v>6966525</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,13 +2428,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827991</t>
+          <t>https://artportalen.se/Sighting/136827990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136827997</v>
+        <v>136827991</v>
       </c>
       <c r="B19" t="n">
         <v>79142</v>
@@ -2465,13 +2469,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413700</v>
+        <v>413902</v>
       </c>
       <c r="R19" t="n">
-        <v>6966474</v>
+        <v>6966496</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,54 +2530,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827997</t>
+          <t>https://artportalen.se/Sighting/136827991</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135784642</v>
+        <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>92267</v>
+        <v>79142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413742</v>
+        <v>413700</v>
       </c>
       <c r="R20" t="n">
-        <v>6966614</v>
+        <v>6966474</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,12 +2601,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2617,27 +2621,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/136827997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136827978</v>
+        <v>135784642</v>
       </c>
       <c r="B21" t="n">
-        <v>92292</v>
+        <v>92267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2665,17 +2669,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>414001</v>
+        <v>413742</v>
       </c>
       <c r="R21" t="n">
-        <v>6966632</v>
+        <v>6966614</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2699,12 +2703,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,65 +2723,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827978</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135784639</v>
+        <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92281</v>
+        <v>92292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1588</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413741</v>
+        <v>414001</v>
       </c>
       <c r="R22" t="n">
-        <v>6966620</v>
+        <v>6966632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2801,12 +2805,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2821,27 +2825,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/136827978</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7000406</v>
+        <v>135784639</v>
       </c>
       <c r="B23" t="n">
-        <v>90932</v>
+        <v>92281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,37 +2853,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>414049</v>
+        <v>413741</v>
       </c>
       <c r="R23" t="n">
-        <v>6966529</v>
+        <v>6966620</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2903,12 +2907,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,31 +2927,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135784649</v>
+        <v>7000406</v>
       </c>
       <c r="B24" t="n">
-        <v>91097</v>
+        <v>90932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,17 +2975,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>413926</v>
+        <v>414049</v>
       </c>
       <c r="R24" t="n">
-        <v>6966725</v>
+        <v>6966529</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3029,27 +3029,31 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120096941</v>
+        <v>135784649</v>
       </c>
       <c r="B25" t="n">
-        <v>91962</v>
+        <v>91097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,34 +3061,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413934</v>
+        <v>413926</v>
       </c>
       <c r="R25" t="n">
-        <v>6966582</v>
+        <v>6966725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,22 +3115,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3141,24 +3135,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096943</v>
+        <v>120096941</v>
       </c>
       <c r="B26" t="n">
         <v>91962</v>
@@ -3193,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413950</v>
+        <v>413934</v>
       </c>
       <c r="R26" t="n">
-        <v>6966665</v>
+        <v>6966582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3228,7 +3222,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3238,7 +3232,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3264,13 +3258,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120096944</v>
+        <v>120096943</v>
       </c>
       <c r="B27" t="n">
         <v>91962</v>
@@ -3305,10 +3299,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413968</v>
+        <v>413950</v>
       </c>
       <c r="R27" t="n">
-        <v>6966758</v>
+        <v>6966665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,7 +3334,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3350,7 +3344,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3376,16 +3370,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136827986</v>
+        <v>120096944</v>
       </c>
       <c r="B28" t="n">
-        <v>92166</v>
+        <v>91962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3417,13 +3411,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413898</v>
+        <v>413968</v>
       </c>
       <c r="R28" t="n">
-        <v>6966645</v>
+        <v>6966758</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3447,12 +3441,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3467,27 +3471,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827986</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135784638</v>
+        <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92010</v>
+        <v>92166</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,37 +3499,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413740</v>
+        <v>413898</v>
       </c>
       <c r="R29" t="n">
-        <v>6966625</v>
+        <v>6966645</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3549,12 +3553,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,49 +3573,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
+          <t>https://artportalen.se/Sighting/136827986</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135784640</v>
+        <v>135784638</v>
       </c>
       <c r="B30" t="n">
-        <v>92051</v>
+        <v>92010</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3625,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>413742</v>
+        <v>413740</v>
       </c>
       <c r="R30" t="n">
-        <v>6966614</v>
+        <v>6966625</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,16 +3686,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
+          <t>https://artportalen.se/Sighting/135784638</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136827989</v>
+        <v>135784640</v>
       </c>
       <c r="B31" t="n">
-        <v>92076</v>
+        <v>92051</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3719,17 +3723,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>413901</v>
+        <v>413742</v>
       </c>
       <c r="R31" t="n">
-        <v>6966581</v>
+        <v>6966614</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3753,12 +3757,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3773,49 +3777,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827989</t>
+          <t>https://artportalen.se/Sighting/135784640</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120096988</v>
+        <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>78730</v>
+        <v>92076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3825,13 +3829,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>413934</v>
+        <v>413901</v>
       </c>
       <c r="R32" t="n">
-        <v>6966582</v>
+        <v>6966581</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3855,22 +3859,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3885,24 +3879,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
+          <t>https://artportalen.se/Sighting/136827989</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120096989</v>
+        <v>120096988</v>
       </c>
       <c r="B33" t="n">
         <v>78730</v>
@@ -3937,10 +3931,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>413968</v>
+        <v>413934</v>
       </c>
       <c r="R33" t="n">
-        <v>6966758</v>
+        <v>6966582</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3972,7 +3966,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3982,7 +3976,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4008,13 +4002,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
+          <t>https://artportalen.se/Sighting/120096988</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120096990</v>
+        <v>120096989</v>
       </c>
       <c r="B34" t="n">
         <v>78730</v>
@@ -4049,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>413973</v>
+        <v>413968</v>
       </c>
       <c r="R34" t="n">
-        <v>6966788</v>
+        <v>6966758</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4084,7 +4078,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4094,7 +4088,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4120,16 +4114,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
+          <t>https://artportalen.se/Sighting/120096989</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135784646</v>
+        <v>120096990</v>
       </c>
       <c r="B35" t="n">
-        <v>78863</v>
+        <v>78730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4157,14 +4151,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>413899</v>
+        <v>413973</v>
       </c>
       <c r="R35" t="n">
-        <v>6966659</v>
+        <v>6966788</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4191,12 +4185,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4211,27 +4215,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
+          <t>https://artportalen.se/Sighting/120096990</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136827983</v>
+        <v>135784646</v>
       </c>
       <c r="B36" t="n">
-        <v>78879</v>
+        <v>78863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4259,17 +4263,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>413867</v>
+        <v>413899</v>
       </c>
       <c r="R36" t="n">
-        <v>6966631</v>
+        <v>6966659</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4293,12 +4297,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4313,27 +4317,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827983</t>
+          <t>https://artportalen.se/Sighting/135784646</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136827995</v>
+        <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>79233</v>
+        <v>78879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4341,21 +4345,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4365,10 +4369,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>413694</v>
+        <v>413867</v>
       </c>
       <c r="R37" t="n">
-        <v>6966470</v>
+        <v>6966631</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4426,16 +4430,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827995</t>
+          <t>https://artportalen.se/Sighting/136827983</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135784635</v>
+        <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>80079</v>
+        <v>79233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4443,37 +4447,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>413755</v>
+        <v>413694</v>
       </c>
       <c r="R38" t="n">
-        <v>6966653</v>
+        <v>6966470</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4497,12 +4501,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4517,24 +4521,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
+          <t>https://artportalen.se/Sighting/136827995</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135784637</v>
+        <v>135784635</v>
       </c>
       <c r="B39" t="n">
         <v>80079</v>
@@ -4569,10 +4573,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>413752</v>
+        <v>413755</v>
       </c>
       <c r="R39" t="n">
-        <v>6966651</v>
+        <v>6966653</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4630,54 +4634,54 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
+          <t>https://artportalen.se/Sighting/135784635</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136827976</v>
+        <v>135784637</v>
       </c>
       <c r="B40" t="n">
-        <v>80595</v>
+        <v>80079</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>414019</v>
+        <v>413752</v>
       </c>
       <c r="R40" t="n">
-        <v>6966614</v>
+        <v>6966651</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4701,12 +4705,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4721,49 +4725,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827976</t>
+          <t>https://artportalen.se/Sighting/135784637</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120096980</v>
+        <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>78334</v>
+        <v>80595</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4773,13 +4777,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>413968</v>
+        <v>414019</v>
       </c>
       <c r="R41" t="n">
-        <v>6966758</v>
+        <v>6966614</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,22 +4807,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4833,27 +4827,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
+          <t>https://artportalen.se/Sighting/136827976</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135784647</v>
+        <v>120096980</v>
       </c>
       <c r="B42" t="n">
-        <v>78464</v>
+        <v>78334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4881,14 +4875,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>413899</v>
+        <v>413968</v>
       </c>
       <c r="R42" t="n">
-        <v>6966658</v>
+        <v>6966758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,12 +4909,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4935,27 +4939,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
+          <t>https://artportalen.se/Sighting/120096980</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136827984</v>
+        <v>135784647</v>
       </c>
       <c r="B43" t="n">
-        <v>58112</v>
+        <v>78464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4963,37 +4967,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6487</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>413898</v>
+        <v>413899</v>
       </c>
       <c r="R43" t="n">
-        <v>6966647</v>
+        <v>6966658</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5017,12 +5021,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5037,24 +5041,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827984</t>
+          <t>https://artportalen.se/Sighting/135784647</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136827993</v>
+        <v>136827984</v>
       </c>
       <c r="B44" t="n">
         <v>58112</v>
@@ -5089,10 +5093,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>413765</v>
+        <v>413898</v>
       </c>
       <c r="R44" t="n">
-        <v>6966461</v>
+        <v>6966647</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5150,38 +5154,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827993</t>
+          <t>https://artportalen.se/Sighting/136827984</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120096936</v>
+        <v>136827993</v>
       </c>
       <c r="B45" t="n">
-        <v>97989</v>
+        <v>58112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5191,13 +5195,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>413957</v>
+        <v>413765</v>
       </c>
       <c r="R45" t="n">
-        <v>6966625</v>
+        <v>6966461</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5221,22 +5225,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5251,62 +5245,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
+          <t>https://artportalen.se/Sighting/136827993</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135784636</v>
+        <v>120096936</v>
       </c>
       <c r="B46" t="n">
-        <v>79218</v>
+        <v>97989</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>413755</v>
+        <v>413957</v>
       </c>
       <c r="R46" t="n">
-        <v>6966653</v>
+        <v>6966625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5333,12 +5327,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5353,24 +5357,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
+          <t>https://artportalen.se/Sighting/120096936</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135784645</v>
+        <v>135784636</v>
       </c>
       <c r="B47" t="n">
         <v>79218</v>
@@ -5405,10 +5409,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>413897</v>
+        <v>413755</v>
       </c>
       <c r="R47" t="n">
-        <v>6966658</v>
+        <v>6966653</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5466,16 +5470,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
+          <t>https://artportalen.se/Sighting/135784636</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136827985</v>
+        <v>135784645</v>
       </c>
       <c r="B48" t="n">
-        <v>79234</v>
+        <v>79218</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5503,17 +5507,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>413903</v>
+        <v>413897</v>
       </c>
       <c r="R48" t="n">
-        <v>6966651</v>
+        <v>6966658</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5537,12 +5541,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5557,27 +5561,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827985</t>
+          <t>https://artportalen.se/Sighting/135784645</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120096926</v>
+        <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79917</v>
+        <v>79234</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5585,21 +5589,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5609,13 +5613,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>413968</v>
+        <v>413903</v>
       </c>
       <c r="R49" t="n">
-        <v>6966758</v>
+        <v>6966651</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5639,22 +5643,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5669,27 +5663,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096926</t>
+          <t>https://artportalen.se/Sighting/136827985</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136827982</v>
+        <v>120096926</v>
       </c>
       <c r="B50" t="n">
-        <v>79499</v>
+        <v>79917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5697,21 +5691,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5721,13 +5715,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>413834</v>
+        <v>413968</v>
       </c>
       <c r="R50" t="n">
-        <v>6966671</v>
+        <v>6966758</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5751,12 +5745,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5771,24 +5775,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827982</t>
+          <t>https://artportalen.se/Sighting/120096926</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136827994</v>
+        <v>136827982</v>
       </c>
       <c r="B51" t="n">
         <v>79499</v>
@@ -5823,10 +5827,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>413748</v>
+        <v>413834</v>
       </c>
       <c r="R51" t="n">
-        <v>6966466</v>
+        <v>6966671</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5883,6 +5887,108 @@
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827982</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136827994</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>413748</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6966466</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136827994</t>
         </is>
@@ -5940,6 +6046,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136827979</v>
+        <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92359</v>
+        <v>92483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413934</v>
+        <v>413901</v>
       </c>
       <c r="R3" t="n">
-        <v>6966721</v>
+        <v>6966647</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827979</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827988</v>
+        <v>136827996</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413901</v>
+        <v>413693</v>
       </c>
       <c r="R4" t="n">
-        <v>6966580</v>
+        <v>6966468</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -980,54 +984,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827988</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136827992</v>
+        <v>7000385</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413901</v>
+        <v>413721</v>
       </c>
       <c r="R5" t="n">
-        <v>6966501</v>
+        <v>6966650</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1075,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827992</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784644</v>
+        <v>7000395</v>
       </c>
       <c r="B6" t="n">
-        <v>92483</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413901</v>
+        <v>413789</v>
       </c>
       <c r="R6" t="n">
-        <v>6966647</v>
+        <v>6966542</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,68 +1181,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136827996</v>
+        <v>7000396</v>
       </c>
       <c r="B7" t="n">
-        <v>92508</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413693</v>
+        <v>413808</v>
       </c>
       <c r="R7" t="n">
-        <v>6966468</v>
+        <v>6966558</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,31 +1281,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827996</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000385</v>
+        <v>7000397</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413721</v>
+        <v>413821</v>
       </c>
       <c r="R8" t="n">
-        <v>6966650</v>
+        <v>6966543</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1366,7 +1378,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,54 +1408,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7000395</v>
+        <v>135784642</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>92267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413789</v>
+        <v>413742</v>
       </c>
       <c r="R9" t="n">
-        <v>6966542</v>
+        <v>6966614</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,31 +1499,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7000396</v>
+        <v>135784639</v>
       </c>
       <c r="B10" t="n">
-        <v>78993</v>
+        <v>92281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413808</v>
+        <v>413741</v>
       </c>
       <c r="R10" t="n">
-        <v>6966558</v>
+        <v>6966620</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1573,12 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,31 +1601,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7000397</v>
+        <v>7000406</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413821</v>
+        <v>414049</v>
       </c>
       <c r="R11" t="n">
-        <v>6966543</v>
+        <v>6966529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,16 +1718,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136827974</v>
+        <v>135784649</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>91097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,37 +1735,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414021</v>
+        <v>413926</v>
       </c>
       <c r="R12" t="n">
-        <v>6966557</v>
+        <v>6966725</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,12 +1789,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,27 +1809,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827974</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136827975</v>
+        <v>120096941</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,13 +1861,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414010</v>
+        <v>413934</v>
       </c>
       <c r="R13" t="n">
-        <v>6966573</v>
+        <v>6966582</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,12 +1891,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,27 +1921,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827975</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136827977</v>
+        <v>120096943</v>
       </c>
       <c r="B14" t="n">
-        <v>79142</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1973,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414020</v>
+        <v>413950</v>
       </c>
       <c r="R14" t="n">
-        <v>6966636</v>
+        <v>6966665</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,12 +2003,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,27 +2033,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827977</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136827980</v>
+        <v>120096944</v>
       </c>
       <c r="B15" t="n">
-        <v>79142</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,13 +2085,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413902</v>
+        <v>413968</v>
       </c>
       <c r="R15" t="n">
-        <v>6966746</v>
+        <v>6966758</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,12 +2115,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,27 +2145,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827980</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136827981</v>
+        <v>135784638</v>
       </c>
       <c r="B16" t="n">
-        <v>79142</v>
+        <v>92010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413888</v>
+        <v>413740</v>
       </c>
       <c r="R16" t="n">
-        <v>6966757</v>
+        <v>6966625</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,12 +2227,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,65 +2247,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827981</t>
+          <t>https://artportalen.se/Sighting/135784638</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136827987</v>
+        <v>135784640</v>
       </c>
       <c r="B17" t="n">
-        <v>79142</v>
+        <v>92051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413928</v>
+        <v>413742</v>
       </c>
       <c r="R17" t="n">
-        <v>6966597</v>
+        <v>6966614</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,12 +2329,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,27 +2349,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827987</t>
+          <t>https://artportalen.se/Sighting/135784640</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136827990</v>
+        <v>120096988</v>
       </c>
       <c r="B18" t="n">
-        <v>79142</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2401,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413884</v>
+        <v>413934</v>
       </c>
       <c r="R18" t="n">
-        <v>6966525</v>
+        <v>6966582</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,12 +2431,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,27 +2461,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827990</t>
+          <t>https://artportalen.se/Sighting/120096988</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136827991</v>
+        <v>120096989</v>
       </c>
       <c r="B19" t="n">
-        <v>79142</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,13 +2513,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413902</v>
+        <v>413968</v>
       </c>
       <c r="R19" t="n">
-        <v>6966496</v>
+        <v>6966758</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,12 +2543,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,27 +2573,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827991</t>
+          <t>https://artportalen.se/Sighting/120096989</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136827997</v>
+        <v>120096990</v>
       </c>
       <c r="B20" t="n">
-        <v>79142</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,13 +2625,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413700</v>
+        <v>413973</v>
       </c>
       <c r="R20" t="n">
-        <v>6966474</v>
+        <v>6966788</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,12 +2655,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,49 +2685,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827997</t>
+          <t>https://artportalen.se/Sighting/120096990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784642</v>
+        <v>135784646</v>
       </c>
       <c r="B21" t="n">
-        <v>92267</v>
+        <v>78863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413742</v>
+        <v>413899</v>
       </c>
       <c r="R21" t="n">
-        <v>6966614</v>
+        <v>6966659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,54 +2798,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/135784646</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136827978</v>
+        <v>135784635</v>
       </c>
       <c r="B22" t="n">
-        <v>92292</v>
+        <v>80079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>414001</v>
+        <v>413755</v>
       </c>
       <c r="R22" t="n">
-        <v>6966632</v>
+        <v>6966653</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,27 +2889,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827978</t>
+          <t>https://artportalen.se/Sighting/135784635</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135784639</v>
+        <v>135784637</v>
       </c>
       <c r="B23" t="n">
-        <v>92281</v>
+        <v>80079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413741</v>
+        <v>413752</v>
       </c>
       <c r="R23" t="n">
-        <v>6966620</v>
+        <v>6966651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,16 +3002,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/135784637</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7000406</v>
+        <v>120096980</v>
       </c>
       <c r="B24" t="n">
-        <v>90932</v>
+        <v>78334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2955,37 +3019,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>414049</v>
+        <v>413968</v>
       </c>
       <c r="R24" t="n">
-        <v>6966529</v>
+        <v>6966758</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,12 +3073,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3029,31 +3103,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/120096980</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135784649</v>
+        <v>135784647</v>
       </c>
       <c r="B25" t="n">
-        <v>91097</v>
+        <v>78464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,21 +3131,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413926</v>
+        <v>413899</v>
       </c>
       <c r="R25" t="n">
-        <v>6966725</v>
+        <v>6966658</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,38 +3216,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/135784647</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096941</v>
+        <v>120096936</v>
       </c>
       <c r="B26" t="n">
-        <v>91962</v>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3257,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413934</v>
+        <v>413957</v>
       </c>
       <c r="R26" t="n">
-        <v>6966582</v>
+        <v>6966625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,7 +3292,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3232,7 +3302,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3258,16 +3328,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/120096936</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120096943</v>
+        <v>135784636</v>
       </c>
       <c r="B27" t="n">
-        <v>91962</v>
+        <v>79218</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,34 +3345,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413950</v>
+        <v>413755</v>
       </c>
       <c r="R27" t="n">
-        <v>6966665</v>
+        <v>6966653</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,22 +3399,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3359,27 +3419,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/135784636</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120096944</v>
+        <v>135784645</v>
       </c>
       <c r="B28" t="n">
-        <v>91962</v>
+        <v>79218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,34 +3447,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413968</v>
+        <v>413897</v>
       </c>
       <c r="R28" t="n">
-        <v>6966758</v>
+        <v>6966658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,22 +3501,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,27 +3521,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/135784645</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136827986</v>
+        <v>120096926</v>
       </c>
       <c r="B29" t="n">
-        <v>92166</v>
+        <v>79917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,13 +3573,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413898</v>
+        <v>413968</v>
       </c>
       <c r="R29" t="n">
-        <v>6966645</v>
+        <v>6966758</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3553,12 +3603,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3573,2424 +3633,18 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827986</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>135784638</v>
-      </c>
-      <c r="B30" t="n">
-        <v>92010</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Chaetodermella luna</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>413740</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6966625</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>135784640</v>
-      </c>
-      <c r="B31" t="n">
-        <v>92051</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>413742</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6966614</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>136827989</v>
-      </c>
-      <c r="B32" t="n">
-        <v>92076</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>413901</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6966581</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827989</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>120096988</v>
-      </c>
-      <c r="B33" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>413934</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6966582</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>120096989</v>
-      </c>
-      <c r="B34" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>120096990</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>413973</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6966788</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135784646</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78863</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>413899</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6966659</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>136827983</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78879</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>413867</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6966631</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827983</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>136827995</v>
-      </c>
-      <c r="B38" t="n">
-        <v>79233</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>413694</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6966470</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827995</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>135784635</v>
-      </c>
-      <c r="B39" t="n">
-        <v>80079</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>413755</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6966653</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135784637</v>
-      </c>
-      <c r="B40" t="n">
-        <v>80079</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>413752</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6966651</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136827976</v>
-      </c>
-      <c r="B41" t="n">
-        <v>80595</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>414019</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6966614</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827976</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>120096980</v>
-      </c>
-      <c r="B42" t="n">
-        <v>78334</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135784647</v>
-      </c>
-      <c r="B43" t="n">
-        <v>78464</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>413899</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6966658</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>136827984</v>
-      </c>
-      <c r="B44" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>413898</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6966647</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827984</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>136827993</v>
-      </c>
-      <c r="B45" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>413765</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6966461</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827993</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>120096936</v>
-      </c>
-      <c r="B46" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>413957</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6966625</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>135784636</v>
-      </c>
-      <c r="B47" t="n">
-        <v>79218</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>413755</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6966653</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135784645</v>
-      </c>
-      <c r="B48" t="n">
-        <v>79218</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>413897</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6966658</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>136827985</v>
-      </c>
-      <c r="B49" t="n">
-        <v>79234</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>413903</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6966651</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827985</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>120096926</v>
-      </c>
-      <c r="B50" t="n">
-        <v>79917</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>136827982</v>
-      </c>
-      <c r="B51" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>413834</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6966671</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827982</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>136827994</v>
-      </c>
-      <c r="B52" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>413748</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6966466</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -6024,29 +3678,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784644</v>
+        <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92483</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413901</v>
+        <v>413934</v>
       </c>
       <c r="R3" t="n">
-        <v>6966647</v>
+        <v>6966721</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/136827979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827996</v>
+        <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92508</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413693</v>
+        <v>413901</v>
       </c>
       <c r="R4" t="n">
-        <v>6966468</v>
+        <v>6966580</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827996</t>
+          <t>https://artportalen.se/Sighting/136827988</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7000385</v>
+        <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413721</v>
+        <v>413901</v>
       </c>
       <c r="R5" t="n">
-        <v>6966650</v>
+        <v>6966501</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,69 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/136827992</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7000395</v>
+        <v>135784644</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>92483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413789</v>
+        <v>413901</v>
       </c>
       <c r="R6" t="n">
-        <v>6966542</v>
+        <v>6966647</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,69 +1173,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7000396</v>
+        <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>92508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413808</v>
+        <v>413693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966558</v>
+        <v>6966468</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,34 +1272,31 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000397</v>
+        <v>7000385</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1343,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413821</v>
+        <v>413721</v>
       </c>
       <c r="R8" t="n">
-        <v>6966543</v>
+        <v>6966650</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,7 +1366,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,54 +1396,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784642</v>
+        <v>7000395</v>
       </c>
       <c r="B9" t="n">
-        <v>92267</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413742</v>
+        <v>413789</v>
       </c>
       <c r="R9" t="n">
-        <v>6966614</v>
+        <v>6966542</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,27 +1487,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784639</v>
+        <v>7000396</v>
       </c>
       <c r="B10" t="n">
-        <v>92281</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,37 +1519,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413741</v>
+        <v>413808</v>
       </c>
       <c r="R10" t="n">
-        <v>6966620</v>
+        <v>6966558</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,27 +1593,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7000406</v>
+        <v>7000397</v>
       </c>
       <c r="B11" t="n">
-        <v>90932</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414049</v>
+        <v>413821</v>
       </c>
       <c r="R11" t="n">
-        <v>6966529</v>
+        <v>6966543</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,16 +1714,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784649</v>
+        <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>91097</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,37 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413926</v>
+        <v>414021</v>
       </c>
       <c r="R12" t="n">
-        <v>6966725</v>
+        <v>6966557</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1789,12 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,27 +1805,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/136827974</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120096941</v>
+        <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>79142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413934</v>
+        <v>414010</v>
       </c>
       <c r="R13" t="n">
-        <v>6966582</v>
+        <v>6966573</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,22 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,27 +1907,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/136827975</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120096943</v>
+        <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>91962</v>
+        <v>79142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413950</v>
+        <v>414020</v>
       </c>
       <c r="R14" t="n">
-        <v>6966665</v>
+        <v>6966636</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,22 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,27 +2009,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/136827977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120096944</v>
+        <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>91962</v>
+        <v>79142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R15" t="n">
-        <v>6966758</v>
+        <v>6966746</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2115,22 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,27 +2111,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/136827980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784638</v>
+        <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>92010</v>
+        <v>79142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2139,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413740</v>
+        <v>413888</v>
       </c>
       <c r="R16" t="n">
-        <v>6966625</v>
+        <v>6966757</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,12 +2193,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,65 +2213,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
+          <t>https://artportalen.se/Sighting/136827981</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135784640</v>
+        <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>92051</v>
+        <v>79142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413742</v>
+        <v>413928</v>
       </c>
       <c r="R17" t="n">
-        <v>6966614</v>
+        <v>6966597</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,12 +2295,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2349,27 +2315,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
+          <t>https://artportalen.se/Sighting/136827987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120096988</v>
+        <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413934</v>
+        <v>413884</v>
       </c>
       <c r="R18" t="n">
-        <v>6966582</v>
+        <v>6966525</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,22 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2461,27 +2417,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
+          <t>https://artportalen.se/Sighting/136827990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120096989</v>
+        <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,13 +2469,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R19" t="n">
-        <v>6966758</v>
+        <v>6966496</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,22 +2499,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,27 +2519,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
+          <t>https://artportalen.se/Sighting/136827991</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120096990</v>
+        <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413973</v>
+        <v>413700</v>
       </c>
       <c r="R20" t="n">
-        <v>6966788</v>
+        <v>6966474</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2655,22 +2601,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,49 +2621,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
+          <t>https://artportalen.se/Sighting/136827997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784646</v>
+        <v>135784642</v>
       </c>
       <c r="B21" t="n">
-        <v>78863</v>
+        <v>92267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413899</v>
+        <v>413742</v>
       </c>
       <c r="R21" t="n">
-        <v>6966659</v>
+        <v>6966614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,54 +2734,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135784635</v>
+        <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>80079</v>
+        <v>92292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413755</v>
+        <v>414001</v>
       </c>
       <c r="R22" t="n">
-        <v>6966653</v>
+        <v>6966632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2869,12 +2805,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,27 +2825,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
+          <t>https://artportalen.se/Sighting/136827978</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135784637</v>
+        <v>135784639</v>
       </c>
       <c r="B23" t="n">
-        <v>80079</v>
+        <v>92281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413752</v>
+        <v>413741</v>
       </c>
       <c r="R23" t="n">
-        <v>6966651</v>
+        <v>6966620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,16 +2938,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120096980</v>
+        <v>7000406</v>
       </c>
       <c r="B24" t="n">
-        <v>78334</v>
+        <v>90932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,37 +2955,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>413968</v>
+        <v>414049</v>
       </c>
       <c r="R24" t="n">
-        <v>6966758</v>
+        <v>6966529</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,22 +3009,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3103,27 +3029,31 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135784647</v>
+        <v>135784649</v>
       </c>
       <c r="B25" t="n">
-        <v>78464</v>
+        <v>91097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3155,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413899</v>
+        <v>413926</v>
       </c>
       <c r="R25" t="n">
-        <v>6966658</v>
+        <v>6966725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,38 +3146,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096936</v>
+        <v>120096941</v>
       </c>
       <c r="B26" t="n">
-        <v>97989</v>
+        <v>91962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3257,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413957</v>
+        <v>413934</v>
       </c>
       <c r="R26" t="n">
-        <v>6966625</v>
+        <v>6966582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,7 +3222,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3302,7 +3232,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,16 +3258,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135784636</v>
+        <v>120096943</v>
       </c>
       <c r="B27" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,34 +3275,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413755</v>
+        <v>413950</v>
       </c>
       <c r="R27" t="n">
-        <v>6966653</v>
+        <v>6966665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,12 +3329,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3419,27 +3359,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135784645</v>
+        <v>120096944</v>
       </c>
       <c r="B28" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,34 +3387,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413897</v>
+        <v>413968</v>
       </c>
       <c r="R28" t="n">
-        <v>6966658</v>
+        <v>6966758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,12 +3441,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,27 +3471,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120096926</v>
+        <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>79917</v>
+        <v>92166</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3573,13 +3523,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413968</v>
+        <v>413898</v>
       </c>
       <c r="R29" t="n">
-        <v>6966758</v>
+        <v>6966645</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3603,22 +3553,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,18 +3573,2424 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136827986</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135784638</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92010</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>413740</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784638</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135784640</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92051</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>413742</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784640</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136827989</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>413901</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6966581</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827989</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120096988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096988</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120096989</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096989</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120096990</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>413973</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6966788</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096990</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135784646</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78863</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6966659</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784646</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136827983</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>413867</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6966631</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827983</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136827995</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>413694</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6966470</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827995</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135784635</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784635</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135784637</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>413752</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784637</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136827976</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>414019</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827976</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120096980</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096980</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135784647</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784647</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136827984</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>413898</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6966647</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827984</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136827993</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>413765</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6966461</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827993</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120096936</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>413957</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096936</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135784636</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784636</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135784645</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>413897</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784645</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136827985</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>413903</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827985</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120096926</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136827982</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>413834</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6966671</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827982</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136827994</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>413748</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6966466</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -3678,6 +6024,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92508</v>
+        <v>92510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92510</v>
+        <v>92512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92512</v>
+        <v>92513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92513</v>
+        <v>92519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136827979</v>
+        <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92370</v>
+        <v>92483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413934</v>
+        <v>413901</v>
       </c>
       <c r="R3" t="n">
-        <v>6966721</v>
+        <v>6966647</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827979</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827988</v>
+        <v>136827996</v>
       </c>
       <c r="B4" t="n">
-        <v>92370</v>
+        <v>92523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413901</v>
+        <v>413693</v>
       </c>
       <c r="R4" t="n">
-        <v>6966580</v>
+        <v>6966468</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -980,54 +984,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827988</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136827992</v>
+        <v>7000385</v>
       </c>
       <c r="B5" t="n">
-        <v>92370</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413901</v>
+        <v>413721</v>
       </c>
       <c r="R5" t="n">
-        <v>6966501</v>
+        <v>6966650</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1075,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827992</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784644</v>
+        <v>7000395</v>
       </c>
       <c r="B6" t="n">
-        <v>92483</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413901</v>
+        <v>413789</v>
       </c>
       <c r="R6" t="n">
-        <v>6966647</v>
+        <v>6966542</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,68 +1181,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136827996</v>
+        <v>7000396</v>
       </c>
       <c r="B7" t="n">
-        <v>92519</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413693</v>
+        <v>413808</v>
       </c>
       <c r="R7" t="n">
-        <v>6966468</v>
+        <v>6966558</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,31 +1281,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827996</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000385</v>
+        <v>7000397</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413721</v>
+        <v>413821</v>
       </c>
       <c r="R8" t="n">
-        <v>6966650</v>
+        <v>6966543</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1366,7 +1378,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,54 +1408,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7000395</v>
+        <v>135784642</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>92267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413789</v>
+        <v>413742</v>
       </c>
       <c r="R9" t="n">
-        <v>6966542</v>
+        <v>6966614</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,31 +1499,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7000396</v>
+        <v>135784639</v>
       </c>
       <c r="B10" t="n">
-        <v>78993</v>
+        <v>92281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413808</v>
+        <v>413741</v>
       </c>
       <c r="R10" t="n">
-        <v>6966558</v>
+        <v>6966620</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1573,12 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,31 +1601,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7000397</v>
+        <v>7000406</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413821</v>
+        <v>414049</v>
       </c>
       <c r="R11" t="n">
-        <v>6966543</v>
+        <v>6966529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,16 +1718,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136827974</v>
+        <v>135784649</v>
       </c>
       <c r="B12" t="n">
-        <v>79149</v>
+        <v>91097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,37 +1735,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414021</v>
+        <v>413926</v>
       </c>
       <c r="R12" t="n">
-        <v>6966557</v>
+        <v>6966725</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,12 +1789,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,27 +1809,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827974</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136827975</v>
+        <v>120096941</v>
       </c>
       <c r="B13" t="n">
-        <v>79149</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,13 +1861,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414010</v>
+        <v>413934</v>
       </c>
       <c r="R13" t="n">
-        <v>6966573</v>
+        <v>6966582</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,12 +1891,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,27 +1921,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827975</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136827977</v>
+        <v>120096943</v>
       </c>
       <c r="B14" t="n">
-        <v>79149</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1973,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414020</v>
+        <v>413950</v>
       </c>
       <c r="R14" t="n">
-        <v>6966636</v>
+        <v>6966665</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,12 +2003,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,27 +2033,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827977</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136827980</v>
+        <v>120096944</v>
       </c>
       <c r="B15" t="n">
-        <v>79149</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,13 +2085,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413902</v>
+        <v>413968</v>
       </c>
       <c r="R15" t="n">
-        <v>6966746</v>
+        <v>6966758</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,12 +2115,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,27 +2145,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827980</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136827981</v>
+        <v>135784638</v>
       </c>
       <c r="B16" t="n">
-        <v>79149</v>
+        <v>92010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413888</v>
+        <v>413740</v>
       </c>
       <c r="R16" t="n">
-        <v>6966757</v>
+        <v>6966625</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,12 +2227,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,65 +2247,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827981</t>
+          <t>https://artportalen.se/Sighting/135784638</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136827987</v>
+        <v>135784640</v>
       </c>
       <c r="B17" t="n">
-        <v>79149</v>
+        <v>92051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413928</v>
+        <v>413742</v>
       </c>
       <c r="R17" t="n">
-        <v>6966597</v>
+        <v>6966614</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,12 +2329,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,27 +2349,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827987</t>
+          <t>https://artportalen.se/Sighting/135784640</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136827990</v>
+        <v>120096988</v>
       </c>
       <c r="B18" t="n">
-        <v>79149</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2401,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413884</v>
+        <v>413934</v>
       </c>
       <c r="R18" t="n">
-        <v>6966525</v>
+        <v>6966582</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,12 +2431,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,27 +2461,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827990</t>
+          <t>https://artportalen.se/Sighting/120096988</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136827991</v>
+        <v>120096989</v>
       </c>
       <c r="B19" t="n">
-        <v>79149</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,13 +2513,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413902</v>
+        <v>413968</v>
       </c>
       <c r="R19" t="n">
-        <v>6966496</v>
+        <v>6966758</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,12 +2543,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,27 +2573,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827991</t>
+          <t>https://artportalen.se/Sighting/120096989</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136827997</v>
+        <v>120096990</v>
       </c>
       <c r="B20" t="n">
-        <v>79149</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,13 +2625,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413700</v>
+        <v>413973</v>
       </c>
       <c r="R20" t="n">
-        <v>6966474</v>
+        <v>6966788</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,12 +2655,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,49 +2685,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827997</t>
+          <t>https://artportalen.se/Sighting/120096990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784642</v>
+        <v>135784646</v>
       </c>
       <c r="B21" t="n">
-        <v>92267</v>
+        <v>78863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413742</v>
+        <v>413899</v>
       </c>
       <c r="R21" t="n">
-        <v>6966614</v>
+        <v>6966659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,54 +2798,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/135784646</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136827978</v>
+        <v>135784635</v>
       </c>
       <c r="B22" t="n">
-        <v>92303</v>
+        <v>80079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>414001</v>
+        <v>413755</v>
       </c>
       <c r="R22" t="n">
-        <v>6966632</v>
+        <v>6966653</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,27 +2889,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827978</t>
+          <t>https://artportalen.se/Sighting/135784635</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135784639</v>
+        <v>135784637</v>
       </c>
       <c r="B23" t="n">
-        <v>92281</v>
+        <v>80079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413741</v>
+        <v>413752</v>
       </c>
       <c r="R23" t="n">
-        <v>6966620</v>
+        <v>6966651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,16 +3002,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/135784637</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7000406</v>
+        <v>120096980</v>
       </c>
       <c r="B24" t="n">
-        <v>90932</v>
+        <v>78334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2955,37 +3019,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>414049</v>
+        <v>413968</v>
       </c>
       <c r="R24" t="n">
-        <v>6966529</v>
+        <v>6966758</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,12 +3073,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3029,31 +3103,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/120096980</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135784649</v>
+        <v>135784647</v>
       </c>
       <c r="B25" t="n">
-        <v>91097</v>
+        <v>78464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,21 +3131,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413926</v>
+        <v>413899</v>
       </c>
       <c r="R25" t="n">
-        <v>6966725</v>
+        <v>6966658</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,38 +3216,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/135784647</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096941</v>
+        <v>120096936</v>
       </c>
       <c r="B26" t="n">
-        <v>91962</v>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3257,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413934</v>
+        <v>413957</v>
       </c>
       <c r="R26" t="n">
-        <v>6966582</v>
+        <v>6966625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,7 +3292,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3232,7 +3302,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3258,16 +3328,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/120096936</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120096943</v>
+        <v>135784636</v>
       </c>
       <c r="B27" t="n">
-        <v>91962</v>
+        <v>79218</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,34 +3345,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413950</v>
+        <v>413755</v>
       </c>
       <c r="R27" t="n">
-        <v>6966665</v>
+        <v>6966653</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,22 +3399,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3359,27 +3419,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/135784636</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120096944</v>
+        <v>135784645</v>
       </c>
       <c r="B28" t="n">
-        <v>91962</v>
+        <v>79218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,34 +3447,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413968</v>
+        <v>413897</v>
       </c>
       <c r="R28" t="n">
-        <v>6966758</v>
+        <v>6966658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,22 +3501,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,27 +3521,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/135784645</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136827986</v>
+        <v>120096926</v>
       </c>
       <c r="B29" t="n">
-        <v>92177</v>
+        <v>79917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,13 +3573,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413898</v>
+        <v>413968</v>
       </c>
       <c r="R29" t="n">
-        <v>6966645</v>
+        <v>6966758</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3553,12 +3603,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3573,2424 +3633,18 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827986</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>135784638</v>
-      </c>
-      <c r="B30" t="n">
-        <v>92010</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Chaetodermella luna</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>413740</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6966625</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>135784640</v>
-      </c>
-      <c r="B31" t="n">
-        <v>92051</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>413742</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6966614</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>136827989</v>
-      </c>
-      <c r="B32" t="n">
-        <v>92087</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>413901</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6966581</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827989</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>120096988</v>
-      </c>
-      <c r="B33" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>413934</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6966582</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>120096989</v>
-      </c>
-      <c r="B34" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>120096990</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>413973</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6966788</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135784646</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78863</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>413899</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6966659</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>136827983</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78886</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>413867</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6966631</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827983</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>136827995</v>
-      </c>
-      <c r="B38" t="n">
-        <v>79240</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>413694</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6966470</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827995</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>135784635</v>
-      </c>
-      <c r="B39" t="n">
-        <v>80079</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>413755</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6966653</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135784637</v>
-      </c>
-      <c r="B40" t="n">
-        <v>80079</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>413752</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6966651</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136827976</v>
-      </c>
-      <c r="B41" t="n">
-        <v>80602</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>414019</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6966614</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827976</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>120096980</v>
-      </c>
-      <c r="B42" t="n">
-        <v>78334</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135784647</v>
-      </c>
-      <c r="B43" t="n">
-        <v>78464</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>413899</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6966658</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>136827984</v>
-      </c>
-      <c r="B44" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>413898</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6966647</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827984</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>136827993</v>
-      </c>
-      <c r="B45" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>413765</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6966461</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827993</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>120096936</v>
-      </c>
-      <c r="B46" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>413957</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6966625</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>135784636</v>
-      </c>
-      <c r="B47" t="n">
-        <v>79218</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>413755</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6966653</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135784645</v>
-      </c>
-      <c r="B48" t="n">
-        <v>79218</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>413897</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6966658</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>136827985</v>
-      </c>
-      <c r="B49" t="n">
-        <v>79241</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>413903</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6966651</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827985</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>120096926</v>
-      </c>
-      <c r="B50" t="n">
-        <v>79917</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>136827982</v>
-      </c>
-      <c r="B51" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>413834</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6966671</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827982</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>136827994</v>
-      </c>
-      <c r="B52" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>413748</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6966466</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -6024,29 +3678,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784644</v>
+        <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92483</v>
+        <v>92374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413901</v>
+        <v>413934</v>
       </c>
       <c r="R3" t="n">
-        <v>6966647</v>
+        <v>6966721</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/136827979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827996</v>
+        <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92523</v>
+        <v>92374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413693</v>
+        <v>413901</v>
       </c>
       <c r="R4" t="n">
-        <v>6966468</v>
+        <v>6966580</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827996</t>
+          <t>https://artportalen.se/Sighting/136827988</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7000385</v>
+        <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>92374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413721</v>
+        <v>413901</v>
       </c>
       <c r="R5" t="n">
-        <v>6966650</v>
+        <v>6966501</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,69 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/136827992</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7000395</v>
+        <v>135784644</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>92483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413789</v>
+        <v>413901</v>
       </c>
       <c r="R6" t="n">
-        <v>6966542</v>
+        <v>6966647</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,69 +1173,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7000396</v>
+        <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>92523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413808</v>
+        <v>413693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966558</v>
+        <v>6966468</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,34 +1272,31 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000397</v>
+        <v>7000385</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1343,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413821</v>
+        <v>413721</v>
       </c>
       <c r="R8" t="n">
-        <v>6966543</v>
+        <v>6966650</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,7 +1366,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,54 +1396,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784642</v>
+        <v>7000395</v>
       </c>
       <c r="B9" t="n">
-        <v>92267</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413742</v>
+        <v>413789</v>
       </c>
       <c r="R9" t="n">
-        <v>6966614</v>
+        <v>6966542</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,27 +1487,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784639</v>
+        <v>7000396</v>
       </c>
       <c r="B10" t="n">
-        <v>92281</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,37 +1519,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413741</v>
+        <v>413808</v>
       </c>
       <c r="R10" t="n">
-        <v>6966620</v>
+        <v>6966558</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,27 +1593,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7000406</v>
+        <v>7000397</v>
       </c>
       <c r="B11" t="n">
-        <v>90932</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414049</v>
+        <v>413821</v>
       </c>
       <c r="R11" t="n">
-        <v>6966529</v>
+        <v>6966543</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,16 +1714,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784649</v>
+        <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>91097</v>
+        <v>79151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,37 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413926</v>
+        <v>414021</v>
       </c>
       <c r="R12" t="n">
-        <v>6966725</v>
+        <v>6966557</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1789,12 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,27 +1805,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/136827974</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120096941</v>
+        <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>79151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413934</v>
+        <v>414010</v>
       </c>
       <c r="R13" t="n">
-        <v>6966582</v>
+        <v>6966573</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,22 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,27 +1907,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/136827975</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120096943</v>
+        <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>91962</v>
+        <v>79151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413950</v>
+        <v>414020</v>
       </c>
       <c r="R14" t="n">
-        <v>6966665</v>
+        <v>6966636</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,22 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,27 +2009,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/136827977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120096944</v>
+        <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>91962</v>
+        <v>79151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R15" t="n">
-        <v>6966758</v>
+        <v>6966746</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2115,22 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,27 +2111,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/136827980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784638</v>
+        <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>92010</v>
+        <v>79151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2139,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413740</v>
+        <v>413888</v>
       </c>
       <c r="R16" t="n">
-        <v>6966625</v>
+        <v>6966757</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,12 +2193,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,65 +2213,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
+          <t>https://artportalen.se/Sighting/136827981</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135784640</v>
+        <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>92051</v>
+        <v>79151</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413742</v>
+        <v>413928</v>
       </c>
       <c r="R17" t="n">
-        <v>6966614</v>
+        <v>6966597</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,12 +2295,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2349,27 +2315,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
+          <t>https://artportalen.se/Sighting/136827987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120096988</v>
+        <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>79151</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413934</v>
+        <v>413884</v>
       </c>
       <c r="R18" t="n">
-        <v>6966582</v>
+        <v>6966525</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,22 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2461,27 +2417,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
+          <t>https://artportalen.se/Sighting/136827990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120096989</v>
+        <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>79151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,13 +2469,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R19" t="n">
-        <v>6966758</v>
+        <v>6966496</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,22 +2499,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,27 +2519,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
+          <t>https://artportalen.se/Sighting/136827991</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120096990</v>
+        <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>78730</v>
+        <v>79151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413973</v>
+        <v>413700</v>
       </c>
       <c r="R20" t="n">
-        <v>6966788</v>
+        <v>6966474</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2655,22 +2601,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,49 +2621,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
+          <t>https://artportalen.se/Sighting/136827997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784646</v>
+        <v>135784642</v>
       </c>
       <c r="B21" t="n">
-        <v>78863</v>
+        <v>92267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413899</v>
+        <v>413742</v>
       </c>
       <c r="R21" t="n">
-        <v>6966659</v>
+        <v>6966614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,54 +2734,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135784635</v>
+        <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>80079</v>
+        <v>92307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413755</v>
+        <v>414001</v>
       </c>
       <c r="R22" t="n">
-        <v>6966653</v>
+        <v>6966632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2869,12 +2805,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,27 +2825,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
+          <t>https://artportalen.se/Sighting/136827978</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135784637</v>
+        <v>135784639</v>
       </c>
       <c r="B23" t="n">
-        <v>80079</v>
+        <v>92281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413752</v>
+        <v>413741</v>
       </c>
       <c r="R23" t="n">
-        <v>6966651</v>
+        <v>6966620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,16 +2938,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120096980</v>
+        <v>7000406</v>
       </c>
       <c r="B24" t="n">
-        <v>78334</v>
+        <v>90932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,37 +2955,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>413968</v>
+        <v>414049</v>
       </c>
       <c r="R24" t="n">
-        <v>6966758</v>
+        <v>6966529</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,22 +3009,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3103,27 +3029,31 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135784647</v>
+        <v>135784649</v>
       </c>
       <c r="B25" t="n">
-        <v>78464</v>
+        <v>91097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3155,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413899</v>
+        <v>413926</v>
       </c>
       <c r="R25" t="n">
-        <v>6966658</v>
+        <v>6966725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,38 +3146,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096936</v>
+        <v>120096941</v>
       </c>
       <c r="B26" t="n">
-        <v>97989</v>
+        <v>91962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3257,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413957</v>
+        <v>413934</v>
       </c>
       <c r="R26" t="n">
-        <v>6966625</v>
+        <v>6966582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,7 +3222,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3302,7 +3232,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,16 +3258,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135784636</v>
+        <v>120096943</v>
       </c>
       <c r="B27" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,34 +3275,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413755</v>
+        <v>413950</v>
       </c>
       <c r="R27" t="n">
-        <v>6966653</v>
+        <v>6966665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,12 +3329,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3419,27 +3359,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135784645</v>
+        <v>120096944</v>
       </c>
       <c r="B28" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,34 +3387,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413897</v>
+        <v>413968</v>
       </c>
       <c r="R28" t="n">
-        <v>6966658</v>
+        <v>6966758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,12 +3441,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,27 +3471,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120096926</v>
+        <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>79917</v>
+        <v>92181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3573,13 +3523,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413968</v>
+        <v>413898</v>
       </c>
       <c r="R29" t="n">
-        <v>6966758</v>
+        <v>6966645</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3603,22 +3553,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,18 +3573,2424 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136827986</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135784638</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92010</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>413740</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784638</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135784640</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92051</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>413742</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784640</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136827989</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92091</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>413901</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6966581</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827989</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120096988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096988</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120096989</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096989</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120096990</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>413973</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6966788</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096990</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135784646</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78863</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6966659</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784646</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136827983</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78888</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>413867</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6966631</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827983</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136827995</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79242</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>413694</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6966470</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827995</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135784635</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784635</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135784637</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>413752</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784637</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136827976</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80604</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>414019</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827976</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120096980</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096980</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135784647</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784647</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136827984</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>413898</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6966647</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827984</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136827993</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>413765</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6966461</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827993</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120096936</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>413957</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096936</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135784636</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784636</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135784645</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>413897</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784645</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136827985</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>413903</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827985</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120096926</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136827982</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>413834</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6966671</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827982</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136827994</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>413748</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6966466</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -3678,6 +6024,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136827979</v>
+        <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92374</v>
+        <v>92483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413934</v>
+        <v>413901</v>
       </c>
       <c r="R3" t="n">
-        <v>6966721</v>
+        <v>6966647</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827979</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827988</v>
+        <v>136827996</v>
       </c>
       <c r="B4" t="n">
-        <v>92374</v>
+        <v>92523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413901</v>
+        <v>413693</v>
       </c>
       <c r="R4" t="n">
-        <v>6966580</v>
+        <v>6966468</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +966,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -980,54 +984,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827988</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136827992</v>
+        <v>7000385</v>
       </c>
       <c r="B5" t="n">
-        <v>92374</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413901</v>
+        <v>413721</v>
       </c>
       <c r="R5" t="n">
-        <v>6966501</v>
+        <v>6966650</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1075,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827992</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135784644</v>
+        <v>7000395</v>
       </c>
       <c r="B6" t="n">
-        <v>92483</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413901</v>
+        <v>413789</v>
       </c>
       <c r="R6" t="n">
-        <v>6966647</v>
+        <v>6966542</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,68 +1181,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136827996</v>
+        <v>7000396</v>
       </c>
       <c r="B7" t="n">
-        <v>92523</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413693</v>
+        <v>413808</v>
       </c>
       <c r="R7" t="n">
-        <v>6966468</v>
+        <v>6966558</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,31 +1281,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827996</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000385</v>
+        <v>7000397</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413721</v>
+        <v>413821</v>
       </c>
       <c r="R8" t="n">
-        <v>6966650</v>
+        <v>6966543</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1366,7 +1378,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,54 +1408,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7000395</v>
+        <v>135784642</v>
       </c>
       <c r="B9" t="n">
-        <v>78993</v>
+        <v>92267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413789</v>
+        <v>413742</v>
       </c>
       <c r="R9" t="n">
-        <v>6966542</v>
+        <v>6966614</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,31 +1499,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7000396</v>
+        <v>135784639</v>
       </c>
       <c r="B10" t="n">
-        <v>78993</v>
+        <v>92281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413808</v>
+        <v>413741</v>
       </c>
       <c r="R10" t="n">
-        <v>6966558</v>
+        <v>6966620</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1573,12 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,31 +1601,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7000397</v>
+        <v>7000406</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413821</v>
+        <v>414049</v>
       </c>
       <c r="R11" t="n">
-        <v>6966543</v>
+        <v>6966529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,16 +1718,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136827974</v>
+        <v>135784649</v>
       </c>
       <c r="B12" t="n">
-        <v>79151</v>
+        <v>91097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,37 +1735,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>414021</v>
+        <v>413926</v>
       </c>
       <c r="R12" t="n">
-        <v>6966557</v>
+        <v>6966725</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,12 +1789,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,27 +1809,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827974</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136827975</v>
+        <v>120096941</v>
       </c>
       <c r="B13" t="n">
-        <v>79151</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,13 +1861,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>414010</v>
+        <v>413934</v>
       </c>
       <c r="R13" t="n">
-        <v>6966573</v>
+        <v>6966582</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,12 +1891,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,27 +1921,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827975</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136827977</v>
+        <v>120096943</v>
       </c>
       <c r="B14" t="n">
-        <v>79151</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1973,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>414020</v>
+        <v>413950</v>
       </c>
       <c r="R14" t="n">
-        <v>6966636</v>
+        <v>6966665</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,12 +2003,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,27 +2033,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827977</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136827980</v>
+        <v>120096944</v>
       </c>
       <c r="B15" t="n">
-        <v>79151</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,13 +2085,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413902</v>
+        <v>413968</v>
       </c>
       <c r="R15" t="n">
-        <v>6966746</v>
+        <v>6966758</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,12 +2115,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,27 +2145,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827980</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136827981</v>
+        <v>135784638</v>
       </c>
       <c r="B16" t="n">
-        <v>79151</v>
+        <v>92010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,37 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413888</v>
+        <v>413740</v>
       </c>
       <c r="R16" t="n">
-        <v>6966757</v>
+        <v>6966625</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,12 +2227,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,65 +2247,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827981</t>
+          <t>https://artportalen.se/Sighting/135784638</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136827987</v>
+        <v>135784640</v>
       </c>
       <c r="B17" t="n">
-        <v>79151</v>
+        <v>92051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413928</v>
+        <v>413742</v>
       </c>
       <c r="R17" t="n">
-        <v>6966597</v>
+        <v>6966614</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,12 +2329,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,27 +2349,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827987</t>
+          <t>https://artportalen.se/Sighting/135784640</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136827990</v>
+        <v>120096988</v>
       </c>
       <c r="B18" t="n">
-        <v>79151</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2401,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413884</v>
+        <v>413934</v>
       </c>
       <c r="R18" t="n">
-        <v>6966525</v>
+        <v>6966582</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,12 +2431,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,27 +2461,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827990</t>
+          <t>https://artportalen.se/Sighting/120096988</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136827991</v>
+        <v>120096989</v>
       </c>
       <c r="B19" t="n">
-        <v>79151</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,13 +2513,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413902</v>
+        <v>413968</v>
       </c>
       <c r="R19" t="n">
-        <v>6966496</v>
+        <v>6966758</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,12 +2543,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,27 +2573,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827991</t>
+          <t>https://artportalen.se/Sighting/120096989</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136827997</v>
+        <v>120096990</v>
       </c>
       <c r="B20" t="n">
-        <v>79151</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,13 +2625,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413700</v>
+        <v>413973</v>
       </c>
       <c r="R20" t="n">
-        <v>6966474</v>
+        <v>6966788</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,12 +2655,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,49 +2685,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827997</t>
+          <t>https://artportalen.se/Sighting/120096990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784642</v>
+        <v>135784646</v>
       </c>
       <c r="B21" t="n">
-        <v>92267</v>
+        <v>78863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413742</v>
+        <v>413899</v>
       </c>
       <c r="R21" t="n">
-        <v>6966614</v>
+        <v>6966659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,54 +2798,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/135784646</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136827978</v>
+        <v>135784635</v>
       </c>
       <c r="B22" t="n">
-        <v>92307</v>
+        <v>80079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>414001</v>
+        <v>413755</v>
       </c>
       <c r="R22" t="n">
-        <v>6966632</v>
+        <v>6966653</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,27 +2889,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827978</t>
+          <t>https://artportalen.se/Sighting/135784635</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135784639</v>
+        <v>135784637</v>
       </c>
       <c r="B23" t="n">
-        <v>92281</v>
+        <v>80079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413741</v>
+        <v>413752</v>
       </c>
       <c r="R23" t="n">
-        <v>6966620</v>
+        <v>6966651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,16 +3002,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/135784637</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7000406</v>
+        <v>120096980</v>
       </c>
       <c r="B24" t="n">
-        <v>90932</v>
+        <v>78334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2955,37 +3019,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>414049</v>
+        <v>413968</v>
       </c>
       <c r="R24" t="n">
-        <v>6966529</v>
+        <v>6966758</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,12 +3073,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3029,31 +3103,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/120096980</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135784649</v>
+        <v>135784647</v>
       </c>
       <c r="B25" t="n">
-        <v>91097</v>
+        <v>78464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,21 +3131,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3155,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413926</v>
+        <v>413899</v>
       </c>
       <c r="R25" t="n">
-        <v>6966725</v>
+        <v>6966658</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,38 +3216,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/135784647</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096941</v>
+        <v>120096936</v>
       </c>
       <c r="B26" t="n">
-        <v>91962</v>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3257,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413934</v>
+        <v>413957</v>
       </c>
       <c r="R26" t="n">
-        <v>6966582</v>
+        <v>6966625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,7 +3292,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3232,7 +3302,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3258,16 +3328,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/120096936</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120096943</v>
+        <v>135784636</v>
       </c>
       <c r="B27" t="n">
-        <v>91962</v>
+        <v>79218</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,34 +3345,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413950</v>
+        <v>413755</v>
       </c>
       <c r="R27" t="n">
-        <v>6966665</v>
+        <v>6966653</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,22 +3399,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3359,27 +3419,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/135784636</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120096944</v>
+        <v>135784645</v>
       </c>
       <c r="B28" t="n">
-        <v>91962</v>
+        <v>79218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,34 +3447,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413968</v>
+        <v>413897</v>
       </c>
       <c r="R28" t="n">
-        <v>6966758</v>
+        <v>6966658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,22 +3501,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,27 +3521,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/135784645</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136827986</v>
+        <v>120096926</v>
       </c>
       <c r="B29" t="n">
-        <v>92181</v>
+        <v>79917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3523,13 +3573,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413898</v>
+        <v>413968</v>
       </c>
       <c r="R29" t="n">
-        <v>6966645</v>
+        <v>6966758</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3553,12 +3603,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3573,2424 +3633,18 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827986</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>135784638</v>
-      </c>
-      <c r="B30" t="n">
-        <v>92010</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Chaetodermella luna</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>413740</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6966625</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>135784640</v>
-      </c>
-      <c r="B31" t="n">
-        <v>92051</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>413742</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6966614</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>136827989</v>
-      </c>
-      <c r="B32" t="n">
-        <v>92091</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>413901</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6966581</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827989</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>120096988</v>
-      </c>
-      <c r="B33" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>413934</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6966582</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>120096989</v>
-      </c>
-      <c r="B34" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>120096990</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78730</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>413973</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6966788</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135784646</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78863</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>413899</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6966659</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>136827983</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78888</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>413867</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6966631</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827983</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>136827995</v>
-      </c>
-      <c r="B38" t="n">
-        <v>79242</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>413694</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6966470</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827995</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>135784635</v>
-      </c>
-      <c r="B39" t="n">
-        <v>80079</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>413755</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6966653</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135784637</v>
-      </c>
-      <c r="B40" t="n">
-        <v>80079</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>413752</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6966651</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136827976</v>
-      </c>
-      <c r="B41" t="n">
-        <v>80604</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>414019</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6966614</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827976</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>120096980</v>
-      </c>
-      <c r="B42" t="n">
-        <v>78334</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135784647</v>
-      </c>
-      <c r="B43" t="n">
-        <v>78464</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>413899</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6966658</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>136827984</v>
-      </c>
-      <c r="B44" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>413898</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6966647</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827984</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>136827993</v>
-      </c>
-      <c r="B45" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>413765</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6966461</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827993</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>120096936</v>
-      </c>
-      <c r="B46" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>413957</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6966625</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>135784636</v>
-      </c>
-      <c r="B47" t="n">
-        <v>79218</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>413755</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6966653</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135784645</v>
-      </c>
-      <c r="B48" t="n">
-        <v>79218</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Putten, Hjd</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>413897</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6966658</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>136827985</v>
-      </c>
-      <c r="B49" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>413903</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6966651</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827985</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>120096926</v>
-      </c>
-      <c r="B50" t="n">
-        <v>79917</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>413968</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6966758</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>136827982</v>
-      </c>
-      <c r="B51" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>413834</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6966671</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827982</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>136827994</v>
-      </c>
-      <c r="B52" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>413748</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6966466</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -6024,29 +3678,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784644</v>
+        <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92483</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413901</v>
+        <v>413934</v>
       </c>
       <c r="R3" t="n">
-        <v>6966647</v>
+        <v>6966721</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784644</t>
+          <t>https://artportalen.se/Sighting/136827979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827996</v>
+        <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92523</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413693</v>
+        <v>413901</v>
       </c>
       <c r="R4" t="n">
-        <v>6966468</v>
+        <v>6966580</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827996</t>
+          <t>https://artportalen.se/Sighting/136827988</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7000385</v>
+        <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>78993</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413721</v>
+        <v>413901</v>
       </c>
       <c r="R5" t="n">
-        <v>6966650</v>
+        <v>6966501</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,69 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/136827992</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7000395</v>
+        <v>135784644</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>92483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413789</v>
+        <v>413901</v>
       </c>
       <c r="R6" t="n">
-        <v>6966542</v>
+        <v>6966647</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,69 +1173,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7000396</v>
+        <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>92525</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413808</v>
+        <v>413693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966558</v>
+        <v>6966468</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,34 +1272,31 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/136827996</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7000397</v>
+        <v>7000385</v>
       </c>
       <c r="B8" t="n">
         <v>78993</v>
@@ -1343,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413821</v>
+        <v>413721</v>
       </c>
       <c r="R8" t="n">
-        <v>6966543</v>
+        <v>6966650</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1378,7 +1366,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,54 +1396,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135784642</v>
+        <v>7000395</v>
       </c>
       <c r="B9" t="n">
-        <v>92267</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413742</v>
+        <v>413789</v>
       </c>
       <c r="R9" t="n">
-        <v>6966614</v>
+        <v>6966542</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,27 +1487,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784642</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135784639</v>
+        <v>7000396</v>
       </c>
       <c r="B10" t="n">
-        <v>92281</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,37 +1519,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413741</v>
+        <v>413808</v>
       </c>
       <c r="R10" t="n">
-        <v>6966620</v>
+        <v>6966558</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,27 +1593,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784639</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7000406</v>
+        <v>7000397</v>
       </c>
       <c r="B11" t="n">
-        <v>90932</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>414049</v>
+        <v>413821</v>
       </c>
       <c r="R11" t="n">
-        <v>6966529</v>
+        <v>6966543</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,16 +1714,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135784649</v>
+        <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>91097</v>
+        <v>79154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,37 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413926</v>
+        <v>414021</v>
       </c>
       <c r="R12" t="n">
-        <v>6966725</v>
+        <v>6966557</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1789,12 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,27 +1805,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784649</t>
+          <t>https://artportalen.se/Sighting/136827974</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120096941</v>
+        <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>79154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413934</v>
+        <v>414010</v>
       </c>
       <c r="R13" t="n">
-        <v>6966582</v>
+        <v>6966573</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1891,22 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,27 +1907,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/136827975</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120096943</v>
+        <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>91962</v>
+        <v>79154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413950</v>
+        <v>414020</v>
       </c>
       <c r="R14" t="n">
-        <v>6966665</v>
+        <v>6966636</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,22 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,27 +2009,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/136827977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120096944</v>
+        <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>91962</v>
+        <v>79154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R15" t="n">
-        <v>6966758</v>
+        <v>6966746</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2115,22 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,27 +2111,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/136827980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135784638</v>
+        <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>92010</v>
+        <v>79154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,37 +2139,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413740</v>
+        <v>413888</v>
       </c>
       <c r="R16" t="n">
-        <v>6966625</v>
+        <v>6966757</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,12 +2193,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,65 +2213,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784638</t>
+          <t>https://artportalen.se/Sighting/136827981</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135784640</v>
+        <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>92051</v>
+        <v>79154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413742</v>
+        <v>413928</v>
       </c>
       <c r="R17" t="n">
-        <v>6966614</v>
+        <v>6966597</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,12 +2295,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2349,27 +2315,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784640</t>
+          <t>https://artportalen.se/Sighting/136827987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120096988</v>
+        <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>79154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413934</v>
+        <v>413884</v>
       </c>
       <c r="R18" t="n">
-        <v>6966582</v>
+        <v>6966525</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,22 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2461,27 +2417,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
+          <t>https://artportalen.se/Sighting/136827990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120096989</v>
+        <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>79154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,13 +2469,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413968</v>
+        <v>413902</v>
       </c>
       <c r="R19" t="n">
-        <v>6966758</v>
+        <v>6966496</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,22 +2499,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,27 +2519,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
+          <t>https://artportalen.se/Sighting/136827991</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120096990</v>
+        <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>78730</v>
+        <v>79154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413973</v>
+        <v>413700</v>
       </c>
       <c r="R20" t="n">
-        <v>6966788</v>
+        <v>6966474</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2655,22 +2601,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,49 +2621,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
+          <t>https://artportalen.se/Sighting/136827997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135784646</v>
+        <v>135784642</v>
       </c>
       <c r="B21" t="n">
-        <v>78863</v>
+        <v>92267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413899</v>
+        <v>413742</v>
       </c>
       <c r="R21" t="n">
-        <v>6966659</v>
+        <v>6966614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,54 +2734,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784646</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135784635</v>
+        <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>80079</v>
+        <v>92309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413755</v>
+        <v>414001</v>
       </c>
       <c r="R22" t="n">
-        <v>6966653</v>
+        <v>6966632</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2869,12 +2805,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,27 +2825,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784635</t>
+          <t>https://artportalen.se/Sighting/136827978</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135784637</v>
+        <v>135784639</v>
       </c>
       <c r="B23" t="n">
-        <v>80079</v>
+        <v>92281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413752</v>
+        <v>413741</v>
       </c>
       <c r="R23" t="n">
-        <v>6966651</v>
+        <v>6966620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,16 +2938,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784637</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120096980</v>
+        <v>7000406</v>
       </c>
       <c r="B24" t="n">
-        <v>78334</v>
+        <v>90932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,37 +2955,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>413968</v>
+        <v>414049</v>
       </c>
       <c r="R24" t="n">
-        <v>6966758</v>
+        <v>6966529</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,22 +3009,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3103,27 +3029,31 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135784647</v>
+        <v>135784649</v>
       </c>
       <c r="B25" t="n">
-        <v>78464</v>
+        <v>91097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3155,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413899</v>
+        <v>413926</v>
       </c>
       <c r="R25" t="n">
-        <v>6966658</v>
+        <v>6966725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,38 +3146,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784647</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120096936</v>
+        <v>120096941</v>
       </c>
       <c r="B26" t="n">
-        <v>97989</v>
+        <v>91962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3257,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413957</v>
+        <v>413934</v>
       </c>
       <c r="R26" t="n">
-        <v>6966625</v>
+        <v>6966582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,7 +3222,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3302,7 +3232,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,16 +3258,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135784636</v>
+        <v>120096943</v>
       </c>
       <c r="B27" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3345,34 +3275,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413755</v>
+        <v>413950</v>
       </c>
       <c r="R27" t="n">
-        <v>6966653</v>
+        <v>6966665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,12 +3329,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3419,27 +3359,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784636</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135784645</v>
+        <v>120096944</v>
       </c>
       <c r="B28" t="n">
-        <v>79218</v>
+        <v>91962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,34 +3387,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413897</v>
+        <v>413968</v>
       </c>
       <c r="R28" t="n">
-        <v>6966658</v>
+        <v>6966758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,12 +3441,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3521,27 +3471,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784645</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120096926</v>
+        <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>79917</v>
+        <v>92183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3499,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3573,13 +3523,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413968</v>
+        <v>413898</v>
       </c>
       <c r="R29" t="n">
-        <v>6966758</v>
+        <v>6966645</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3603,22 +3553,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,18 +3573,2424 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136827986</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135784638</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92010</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>413740</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784638</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135784640</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92051</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>413742</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784640</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136827989</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92093</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>413901</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6966581</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827989</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120096988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096988</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120096989</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096989</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120096990</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>413973</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6966788</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096990</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135784646</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78863</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6966659</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784646</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136827983</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78891</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>413867</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6966631</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827983</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136827995</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79245</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>413694</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6966470</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827995</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135784635</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784635</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135784637</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>413752</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784637</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136827976</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80607</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>414019</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827976</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120096980</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096980</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135784647</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78464</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784647</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136827984</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>413898</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6966647</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827984</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136827993</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>413765</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6966461</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827993</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120096936</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>413957</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096936</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135784636</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784636</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135784645</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79218</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>413897</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784645</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136827985</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>413903</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827985</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120096926</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120096926</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136827982</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>413834</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6966671</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827982</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136827994</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>413748</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6966466</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827994</t>
         </is>
       </c>
     </row>
@@ -3678,6 +6024,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92525</v>
+        <v>92538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136827984</v>
       </c>
       <c r="B44" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136827993</v>
       </c>
       <c r="B45" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136827984</v>
       </c>
       <c r="B44" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136827993</v>
       </c>
       <c r="B45" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92543</v>
+        <v>92553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136827984</v>
       </c>
       <c r="B44" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136827993</v>
       </c>
       <c r="B45" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92553</v>
+        <v>92554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136827984</v>
       </c>
       <c r="B44" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136827993</v>
       </c>
       <c r="B45" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92557</v>
+        <v>92559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92559</v>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136827984</v>
       </c>
       <c r="B44" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>136827993</v>
       </c>
       <c r="B45" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136827979</v>
       </c>
       <c r="B3" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136827988</v>
       </c>
       <c r="B4" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136827992</v>
       </c>
       <c r="B5" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92564</v>
+        <v>92576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136827974</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136827975</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136827977</v>
       </c>
       <c r="B14" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136827980</v>
       </c>
       <c r="B15" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136827981</v>
       </c>
       <c r="B16" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>136827987</v>
       </c>
       <c r="B17" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>136827990</v>
       </c>
       <c r="B18" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>136827991</v>
       </c>
       <c r="B19" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>136827997</v>
       </c>
       <c r="B20" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136827978</v>
       </c>
       <c r="B22" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136827986</v>
       </c>
       <c r="B29" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>136827989</v>
       </c>
       <c r="B32" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>136827983</v>
       </c>
       <c r="B37" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>136827995</v>
       </c>
       <c r="B38" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>136827976</v>
       </c>
       <c r="B41" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136827985</v>
       </c>
       <c r="B49" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>136827982</v>
       </c>
       <c r="B51" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>136827994</v>
       </c>
       <c r="B52" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92576</v>
+        <v>92577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>136827996</v>
       </c>
       <c r="B7" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
